--- a/data.xlsx
+++ b/data.xlsx
@@ -14,15 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>年份</t>
   </si>
   <si>
-    <t>单位名称</t>
+    <t>我去</t>
   </si>
   <si>
-    <t>金额</t>
+    <t>预算</t>
   </si>
   <si>
     <t>日期</t>
@@ -31,48 +31,34 @@
     <t>文件标题</t>
   </si>
   <si>
-    <t>score</t>
-  </si>
-  <si>
-    <t>company_logo</t>
-  </si>
-  <si>
-    <t>测试部门</t>
+    <t>管理中心</t>
   </si>
   <si>
     <t>测试标题</t>
   </si>
   <si>
-    <t>img.png</t>
-  </si>
-  <si>
-    <t>人力部</t>
+    <t>开发中心</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="仿宋"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -527,10 +513,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -539,33 +525,36 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -575,111 +564,105 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1001,14 +984,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="13.75"/>
     <col min="4" max="4" width="14.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.75" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1024,51 +1006,36 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1233454</v>
-      </c>
-      <c r="D2" s="3">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>123</v>
+      </c>
+      <c r="D2" s="1">
         <v>46260</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>90</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>23523</v>
-      </c>
-      <c r="D3" s="3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>456</v>
+      </c>
+      <c r="D3" s="2">
         <v>46260</v>
-      </c>
-      <c r="F3">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
